--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/2732-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/2732-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FD954467-1562-481B-B878-0F2DD7826877}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9C10DD9C-2FE8-4E20-A40A-E4D2D002C93B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{EE0BE52C-7B97-46DC-8976-BAB745454353}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{7CF7CFD6-7D36-4720-BC3A-541C819CC7D9}"/>
   </bookViews>
   <sheets>
     <sheet name="2732-dividend-20260225_0_4" sheetId="1" r:id="rId1"/>
@@ -1523,23 +1523,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5625840B-FAF5-4948-8F7E-A1C8DDC4DA1E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81250239-32F0-4984-9A79-75FCF86D7D1A}">
   <dimension ref="A1:R43"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="7.33203125" customWidth="1"/>
-    <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="7" width="8.33203125" customWidth="1"/>
-    <col min="8" max="8" width="8" customWidth="1"/>
-    <col min="9" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="8.77734375" customWidth="1"/>
+    <col min="1" max="1" width="6.5" customWidth="1"/>
+    <col min="2" max="2" width="9.25" customWidth="1"/>
+    <col min="3" max="3" width="10" customWidth="1"/>
+    <col min="4" max="7" width="10.5" customWidth="1"/>
+    <col min="8" max="8" width="10" customWidth="1"/>
+    <col min="9" max="10" width="10.5" customWidth="1"/>
+    <col min="11" max="13" width="10" customWidth="1"/>
+    <col min="14" max="14" width="10.5" customWidth="1"/>
+    <col min="15" max="17" width="10" customWidth="1"/>
+    <col min="18" max="18" width="10.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1567,7 +1567,7 @@
       <c r="Q1" s="30"/>
       <c r="R1" s="22"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1597,7 +1597,7 @@
       <c r="Q2" s="32"/>
       <c r="R2" s="33"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1643,7 +1643,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1693,7 +1693,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="37">
         <v>2025</v>
       </c>
@@ -1747,7 +1747,7 @@
         <v>4.74</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>25</v>
       </c>
@@ -1803,7 +1803,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>25</v>
       </c>
@@ -1859,7 +1859,7 @@
         <v>1.98</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
         <v>25</v>
       </c>
@@ -1915,7 +1915,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
         <v>25</v>
       </c>
@@ -1971,7 +1971,7 @@
         <v>2.76</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="39">
         <v>2024</v>
       </c>
@@ -2025,7 +2025,7 @@
         <v>5.01</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="17" t="s">
         <v>25</v>
       </c>
@@ -2081,7 +2081,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="17" t="s">
         <v>25</v>
       </c>
@@ -2137,7 +2137,7 @@
         <v>2.35</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="17" t="s">
         <v>25</v>
       </c>
@@ -2193,7 +2193,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="17" t="s">
         <v>25</v>
       </c>
@@ -2249,7 +2249,7 @@
         <v>2.66</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="37">
         <v>2023</v>
       </c>
@@ -2303,7 +2303,7 @@
         <v>4.74</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
         <v>25</v>
       </c>
@@ -2359,7 +2359,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>25</v>
       </c>
@@ -2415,7 +2415,7 @@
         <v>2.37</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
         <v>25</v>
       </c>
@@ -2471,7 +2471,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>25</v>
       </c>
@@ -2527,7 +2527,7 @@
         <v>2.37</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="39">
         <v>2022</v>
       </c>
@@ -2581,7 +2581,7 @@
         <v>4.07</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="17" t="s">
         <v>25</v>
       </c>
@@ -2637,7 +2637,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="17" t="s">
         <v>25</v>
       </c>
@@ -2693,7 +2693,7 @@
         <v>1.95</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="17" t="s">
         <v>25</v>
       </c>
@@ -2749,7 +2749,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="17" t="s">
         <v>25</v>
       </c>
@@ -2805,7 +2805,7 @@
         <v>2.12</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="17" t="s">
         <v>25</v>
       </c>
@@ -2861,7 +2861,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="17" t="s">
         <v>25</v>
       </c>
@@ -2917,7 +2917,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="37">
         <v>2021</v>
       </c>
@@ -2971,7 +2971,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="11" t="s">
         <v>25</v>
       </c>
@@ -3027,7 +3027,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
         <v>25</v>
       </c>
@@ -3083,7 +3083,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="11" t="s">
         <v>25</v>
       </c>
@@ -3139,7 +3139,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="11" t="s">
         <v>25</v>
       </c>
@@ -3195,7 +3195,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="39">
         <v>2020</v>
       </c>
@@ -3249,7 +3249,7 @@
         <v>5.3</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="17" t="s">
         <v>25</v>
       </c>
@@ -3305,7 +3305,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="17" t="s">
         <v>25</v>
       </c>
@@ -3361,7 +3361,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="17" t="s">
         <v>25</v>
       </c>
@@ -3417,7 +3417,7 @@
         <v>5.3</v>
       </c>
     </row>
-    <row r="36" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="37">
         <v>2019</v>
       </c>
@@ -3471,7 +3471,7 @@
         <v>2.94</v>
       </c>
     </row>
-    <row r="37" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="39">
         <v>2018</v>
       </c>
@@ -3525,7 +3525,7 @@
         <v>5.01</v>
       </c>
     </row>
-    <row r="38" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="37">
         <v>2017</v>
       </c>
@@ -3579,7 +3579,7 @@
         <v>5.46</v>
       </c>
     </row>
-    <row r="39" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="39">
         <v>2016</v>
       </c>
@@ -3633,7 +3633,7 @@
         <v>6.07</v>
       </c>
     </row>
-    <row r="40" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="37">
         <v>2015</v>
       </c>
@@ -3687,7 +3687,7 @@
         <v>4.43</v>
       </c>
     </row>
-    <row r="41" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="39">
         <v>2014</v>
       </c>
@@ -3741,7 +3741,7 @@
         <v>2.46</v>
       </c>
     </row>
-    <row r="42" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="37">
         <v>2013</v>
       </c>
@@ -3795,7 +3795,7 @@
         <v>2.91</v>
       </c>
     </row>
-    <row r="43" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A43" s="39" t="s">
         <v>60</v>
       </c>
